--- a/IT23754270 Assignment 1 - Test cases.xlsx
+++ b/IT23754270 Assignment 1 - Test cases.xlsx
@@ -696,14 +696,10 @@
           <t>මේක දැන්ම කරන්න</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>මේක දැන්ම කරන්න</t>
-        </is>
-      </c>
+      <c r="E10" s="3" t="inlineStr"/>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>

--- a/IT23754270 Assignment 1 - Test cases.xlsx
+++ b/IT23754270 Assignment 1 - Test cases.xlsx
@@ -727,7 +727,7 @@
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>UI Error</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>

--- a/IT23754270 Assignment 1 - Test cases.xlsx
+++ b/IT23754270 Assignment 1 - Test cases.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MSI\Downloads\test_automation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MSI\Downloads\test_automation (2)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE504D65-6903-47EB-A55A-4BA1A189EFD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD27E44C-B524-41BB-988B-B45151DDF15B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="722" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="304">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -931,6 +931,9 @@
   </si>
   <si>
     <t>Evidence: The long input contains “8:30AM”, “Google Meet”, “online class”, “mic”, “notes”, and “notebook”.</t>
+  </si>
+  <si>
+    <t>මම 6.30pm වලට වගේ පාරට එන්නම්, ඔයත් එන්න.</t>
   </si>
 </sst>
 </file>
@@ -1042,7 +1045,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1081,8 +1084,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1418,7 +1420,7 @@
       <c r="D2" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>12</v>
       </c>
       <c r="F2" s="10" t="s">
@@ -1444,7 +1446,7 @@
       <c r="D3" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="17" t="s">
         <v>19</v>
       </c>
       <c r="F3" s="10" t="s">
@@ -1574,7 +1576,7 @@
       <c r="D8" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="3" t="s">
         <v>49</v>
       </c>
       <c r="F8" s="3" t="s">
@@ -2376,7 +2378,7 @@
         <v>229</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>229</v>
+        <v>303</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>230</v>
